--- a/pantallas_android/catalogo_parametros_del_mantenimiento_hvac_actualizado.xlsx
+++ b/pantallas_android/catalogo_parametros_del_mantenimiento_hvac_actualizado.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uuario\Documents\workspace\cursoAndroid\pantallas_android\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1A1A35-8484-4283-B6E6-1A37F9F2246C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>
@@ -29,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ParametrosTecnicos!$A$1:$F$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ValoresEquipo!$A$1:$K$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -2202,8 +2196,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2566,19 +2560,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G568"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2601,7 +2596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2621,7 +2616,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2641,7 +2636,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2661,7 +2656,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2684,7 +2679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2704,7 +2699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2724,7 +2719,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2744,7 +2739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2767,7 +2762,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2790,7 +2785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2810,7 +2805,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2830,7 +2825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2850,7 +2845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2870,7 +2865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2893,7 +2888,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2916,7 +2911,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2939,7 +2934,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2962,7 +2957,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2985,7 +2980,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3008,7 +3003,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3031,7 +3026,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3054,7 +3049,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3077,7 +3072,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3097,7 +3092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3120,7 +3115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3140,7 +3135,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3160,7 +3155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3180,7 +3175,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3203,7 +3198,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3226,7 +3221,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3249,7 +3244,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3269,7 +3264,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3289,7 +3284,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3312,7 +3307,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3332,7 +3327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3352,7 +3347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3372,7 +3367,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3392,7 +3387,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3412,7 +3407,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3432,7 +3427,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3455,7 +3450,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3475,7 +3470,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3495,7 +3490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3515,7 +3510,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3538,7 +3533,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3558,7 +3553,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3578,7 +3573,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3598,7 +3593,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3618,7 +3613,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3638,7 +3633,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3658,7 +3653,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3678,7 +3673,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3698,7 +3693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3718,7 +3713,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3738,7 +3733,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3758,7 +3753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3778,7 +3773,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3798,7 +3793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3818,7 +3813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3838,7 +3833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3858,7 +3853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3878,7 +3873,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3898,7 +3893,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3918,7 +3913,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3938,7 +3933,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3958,7 +3953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3978,7 +3973,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3998,7 +3993,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4018,7 +4013,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4041,7 +4036,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4064,7 +4059,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4087,7 +4082,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4110,7 +4105,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4133,7 +4128,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4156,7 +4151,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4179,7 +4174,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4202,7 +4197,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4225,7 +4220,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4245,7 +4240,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4265,7 +4260,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4285,7 +4280,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4305,7 +4300,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4325,7 +4320,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4345,7 +4340,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4365,7 +4360,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4385,7 +4380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4405,7 +4400,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4425,7 +4420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4445,7 +4440,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4465,7 +4460,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4485,7 +4480,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4505,7 +4500,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4525,7 +4520,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4545,7 +4540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4565,7 +4560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4585,7 +4580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4605,7 +4600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4625,7 +4620,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4645,7 +4640,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4665,7 +4660,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4685,7 +4680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102">
         <v>101</v>
       </c>
@@ -4705,7 +4700,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103">
         <v>102</v>
       </c>
@@ -4725,7 +4720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104">
         <v>103</v>
       </c>
@@ -4745,7 +4740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105">
         <v>104</v>
       </c>
@@ -4765,7 +4760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106">
         <v>105</v>
       </c>
@@ -4785,7 +4780,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107">
         <v>106</v>
       </c>
@@ -4805,7 +4800,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108">
         <v>107</v>
       </c>
@@ -4825,7 +4820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109">
         <v>108</v>
       </c>
@@ -4845,7 +4840,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110">
         <v>109</v>
       </c>
@@ -4865,7 +4860,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111">
         <v>110</v>
       </c>
@@ -4885,7 +4880,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112">
         <v>111</v>
       </c>
@@ -4905,7 +4900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7">
       <c r="A113">
         <v>112</v>
       </c>
@@ -4928,7 +4923,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7">
       <c r="A114">
         <v>113</v>
       </c>
@@ -4948,7 +4943,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7">
       <c r="A115">
         <v>114</v>
       </c>
@@ -4968,7 +4963,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7">
       <c r="A116">
         <v>115</v>
       </c>
@@ -4991,7 +4986,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5014,7 +5009,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7">
       <c r="A118">
         <v>117</v>
       </c>
@@ -5037,7 +5032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5060,7 +5055,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7">
       <c r="A120">
         <v>119</v>
       </c>
@@ -5083,7 +5078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5106,7 +5101,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5129,7 +5124,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7">
       <c r="A123">
         <v>122</v>
       </c>
@@ -5152,7 +5147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7">
       <c r="A124">
         <v>123</v>
       </c>
@@ -5175,7 +5170,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125">
         <v>124</v>
       </c>
@@ -5198,7 +5193,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126">
         <v>125</v>
       </c>
@@ -5221,7 +5216,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7">
       <c r="A127">
         <v>126</v>
       </c>
@@ -5244,7 +5239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7">
       <c r="A128">
         <v>127</v>
       </c>
@@ -5267,7 +5262,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7">
       <c r="A129">
         <v>128</v>
       </c>
@@ -5290,7 +5285,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7">
       <c r="A130">
         <v>129</v>
       </c>
@@ -5313,7 +5308,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7">
       <c r="A131">
         <v>130</v>
       </c>
@@ -5333,7 +5328,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7">
       <c r="A132">
         <v>131</v>
       </c>
@@ -5353,7 +5348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7">
       <c r="A133">
         <v>132</v>
       </c>
@@ -5373,7 +5368,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>133</v>
       </c>
@@ -5393,7 +5388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>134</v>
       </c>
@@ -5413,7 +5408,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>135</v>
       </c>
@@ -5436,7 +5431,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7">
       <c r="A137">
         <v>136</v>
       </c>
@@ -5459,7 +5454,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7">
       <c r="A138">
         <v>137</v>
       </c>
@@ -5482,7 +5477,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7">
       <c r="A139">
         <v>138</v>
       </c>
@@ -5502,7 +5497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7">
       <c r="A140">
         <v>139</v>
       </c>
@@ -5522,7 +5517,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7">
       <c r="A141">
         <v>140</v>
       </c>
@@ -5542,7 +5537,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>141</v>
       </c>
@@ -5562,7 +5557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7">
       <c r="A143">
         <v>142</v>
       </c>
@@ -5582,7 +5577,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7">
       <c r="A144">
         <v>143</v>
       </c>
@@ -5602,7 +5597,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7">
       <c r="A145">
         <v>144</v>
       </c>
@@ -5622,7 +5617,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7">
       <c r="A146">
         <v>145</v>
       </c>
@@ -5642,7 +5637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7">
       <c r="A147">
         <v>146</v>
       </c>
@@ -5662,7 +5657,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7">
       <c r="A148">
         <v>147</v>
       </c>
@@ -5685,7 +5680,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7">
       <c r="A149">
         <v>148</v>
       </c>
@@ -5705,7 +5700,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7">
       <c r="A150">
         <v>149</v>
       </c>
@@ -5725,7 +5720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7">
       <c r="A151">
         <v>150</v>
       </c>
@@ -5745,7 +5740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7">
       <c r="A152">
         <v>151</v>
       </c>
@@ -5765,7 +5760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7">
       <c r="A153">
         <v>152</v>
       </c>
@@ -5785,7 +5780,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7">
       <c r="A154">
         <v>153</v>
       </c>
@@ -5805,7 +5800,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7">
       <c r="A155">
         <v>154</v>
       </c>
@@ -5825,7 +5820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7">
       <c r="A156">
         <v>155</v>
       </c>
@@ -5845,7 +5840,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7">
       <c r="A157">
         <v>156</v>
       </c>
@@ -5865,7 +5860,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7">
       <c r="A158">
         <v>157</v>
       </c>
@@ -5885,7 +5880,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7">
       <c r="A159">
         <v>158</v>
       </c>
@@ -5905,7 +5900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7">
       <c r="A160">
         <v>159</v>
       </c>
@@ -5925,7 +5920,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7">
       <c r="A161">
         <v>160</v>
       </c>
@@ -5945,7 +5940,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7">
       <c r="A162">
         <v>161</v>
       </c>
@@ -5965,7 +5960,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7">
       <c r="A163">
         <v>162</v>
       </c>
@@ -5985,7 +5980,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7">
       <c r="A164">
         <v>163</v>
       </c>
@@ -6005,7 +6000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7">
       <c r="A165">
         <v>164</v>
       </c>
@@ -6025,7 +6020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7">
       <c r="A166">
         <v>165</v>
       </c>
@@ -6048,7 +6043,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7">
       <c r="A167">
         <v>166</v>
       </c>
@@ -6068,7 +6063,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7">
       <c r="A168">
         <v>167</v>
       </c>
@@ -6088,7 +6083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7">
       <c r="A169">
         <v>168</v>
       </c>
@@ -6108,7 +6103,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7">
       <c r="A170">
         <v>169</v>
       </c>
@@ -6128,7 +6123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7">
       <c r="A171">
         <v>170</v>
       </c>
@@ -6148,7 +6143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7">
       <c r="A172">
         <v>171</v>
       </c>
@@ -6168,7 +6163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7">
       <c r="A173">
         <v>172</v>
       </c>
@@ -6188,7 +6183,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7">
       <c r="A174">
         <v>173</v>
       </c>
@@ -6208,7 +6203,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7">
       <c r="A175">
         <v>174</v>
       </c>
@@ -6228,7 +6223,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7">
       <c r="A176">
         <v>175</v>
       </c>
@@ -6248,7 +6243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6">
       <c r="A177">
         <v>176</v>
       </c>
@@ -6268,7 +6263,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6">
       <c r="A178">
         <v>177</v>
       </c>
@@ -6288,7 +6283,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6">
       <c r="A179">
         <v>178</v>
       </c>
@@ -6308,7 +6303,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6">
       <c r="A180">
         <v>179</v>
       </c>
@@ -6328,7 +6323,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6">
       <c r="A181">
         <v>180</v>
       </c>
@@ -6348,7 +6343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6">
       <c r="A182">
         <v>181</v>
       </c>
@@ -6368,7 +6363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6">
       <c r="A183">
         <v>182</v>
       </c>
@@ -6388,7 +6383,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6">
       <c r="A184">
         <v>183</v>
       </c>
@@ -6408,7 +6403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6">
       <c r="A185">
         <v>184</v>
       </c>
@@ -6428,7 +6423,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6">
       <c r="A186">
         <v>185</v>
       </c>
@@ -6448,7 +6443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6">
       <c r="A187">
         <v>186</v>
       </c>
@@ -6468,7 +6463,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6">
       <c r="A188">
         <v>187</v>
       </c>
@@ -6488,7 +6483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6">
       <c r="A189">
         <v>188</v>
       </c>
@@ -6508,7 +6503,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6">
       <c r="A190">
         <v>189</v>
       </c>
@@ -6528,7 +6523,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6">
       <c r="A191">
         <v>190</v>
       </c>
@@ -6548,7 +6543,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6">
       <c r="A192">
         <v>191</v>
       </c>
@@ -6568,7 +6563,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7">
       <c r="A193">
         <v>192</v>
       </c>
@@ -6591,7 +6586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7">
       <c r="A194">
         <v>193</v>
       </c>
@@ -6611,7 +6606,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7">
       <c r="A195">
         <v>194</v>
       </c>
@@ -6631,7 +6626,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7">
       <c r="A196">
         <v>195</v>
       </c>
@@ -6651,7 +6646,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7">
       <c r="A197">
         <v>196</v>
       </c>
@@ -6671,7 +6666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7">
       <c r="A198">
         <v>197</v>
       </c>
@@ -6694,7 +6689,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7">
       <c r="A199">
         <v>198</v>
       </c>
@@ -6714,7 +6709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7">
       <c r="A200">
         <v>199</v>
       </c>
@@ -6737,7 +6732,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7">
       <c r="A201">
         <v>200</v>
       </c>
@@ -6760,7 +6755,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7">
       <c r="A202">
         <v>201</v>
       </c>
@@ -6783,7 +6778,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7">
       <c r="A203">
         <v>202</v>
       </c>
@@ -6806,7 +6801,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7">
       <c r="A204">
         <v>203</v>
       </c>
@@ -6826,7 +6821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7">
       <c r="A205">
         <v>204</v>
       </c>
@@ -6849,7 +6844,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7">
       <c r="A206">
         <v>205</v>
       </c>
@@ -6872,7 +6867,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7">
       <c r="A207">
         <v>206</v>
       </c>
@@ -6892,7 +6887,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7">
       <c r="A208">
         <v>207</v>
       </c>
@@ -6912,7 +6907,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7">
       <c r="A209">
         <v>208</v>
       </c>
@@ -6932,7 +6927,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7">
       <c r="A210">
         <v>209</v>
       </c>
@@ -6952,7 +6947,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7">
       <c r="A211">
         <v>210</v>
       </c>
@@ -6972,7 +6967,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7">
       <c r="A212">
         <v>211</v>
       </c>
@@ -6992,7 +6987,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7">
       <c r="A213">
         <v>212</v>
       </c>
@@ -7012,7 +7007,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7">
       <c r="A214">
         <v>213</v>
       </c>
@@ -7032,7 +7027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7">
       <c r="A215">
         <v>214</v>
       </c>
@@ -7052,7 +7047,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7">
       <c r="A216">
         <v>215</v>
       </c>
@@ -7072,7 +7067,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7">
       <c r="A217">
         <v>216</v>
       </c>
@@ -7095,7 +7090,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7">
       <c r="A218">
         <v>217</v>
       </c>
@@ -7118,7 +7113,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7">
       <c r="A219">
         <v>218</v>
       </c>
@@ -7138,7 +7133,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7">
       <c r="A220">
         <v>219</v>
       </c>
@@ -7161,7 +7156,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7">
       <c r="A221">
         <v>220</v>
       </c>
@@ -7184,7 +7179,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7">
       <c r="A222">
         <v>221</v>
       </c>
@@ -7207,7 +7202,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7">
       <c r="A223">
         <v>222</v>
       </c>
@@ -7227,7 +7222,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7">
       <c r="A224">
         <v>223</v>
       </c>
@@ -7247,7 +7242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7">
       <c r="A225">
         <v>224</v>
       </c>
@@ -7267,7 +7262,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7">
       <c r="A226">
         <v>225</v>
       </c>
@@ -7287,7 +7282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7">
       <c r="A227">
         <v>226</v>
       </c>
@@ -7307,7 +7302,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7">
       <c r="A228">
         <v>227</v>
       </c>
@@ -7327,7 +7322,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7">
       <c r="A229">
         <v>228</v>
       </c>
@@ -7347,7 +7342,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7">
       <c r="A230">
         <v>229</v>
       </c>
@@ -7370,7 +7365,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7">
       <c r="A231">
         <v>230</v>
       </c>
@@ -7390,7 +7385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7">
       <c r="A232">
         <v>231</v>
       </c>
@@ -7413,7 +7408,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7">
       <c r="A233">
         <v>232</v>
       </c>
@@ -7436,7 +7431,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7">
       <c r="A234">
         <v>233</v>
       </c>
@@ -7456,7 +7451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7">
       <c r="A235">
         <v>234</v>
       </c>
@@ -7476,7 +7471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7">
       <c r="A236">
         <v>235</v>
       </c>
@@ -7496,7 +7491,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7">
       <c r="A237">
         <v>236</v>
       </c>
@@ -7516,7 +7511,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7">
       <c r="A238">
         <v>237</v>
       </c>
@@ -7536,7 +7531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7">
       <c r="A239">
         <v>238</v>
       </c>
@@ -7556,7 +7551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7">
       <c r="A240">
         <v>239</v>
       </c>
@@ -7576,7 +7571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7">
       <c r="A241">
         <v>240</v>
       </c>
@@ -7596,7 +7591,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7">
       <c r="A242">
         <v>241</v>
       </c>
@@ -7616,7 +7611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7">
       <c r="A243">
         <v>242</v>
       </c>
@@ -7636,7 +7631,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7">
       <c r="A244">
         <v>243</v>
       </c>
@@ -7659,7 +7654,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7">
       <c r="A245">
         <v>244</v>
       </c>
@@ -7682,7 +7677,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7">
       <c r="A246">
         <v>245</v>
       </c>
@@ -7702,7 +7697,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7">
       <c r="A247">
         <v>246</v>
       </c>
@@ -7725,7 +7720,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7">
       <c r="A248">
         <v>247</v>
       </c>
@@ -7748,7 +7743,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7">
       <c r="A249">
         <v>248</v>
       </c>
@@ -7771,7 +7766,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7">
       <c r="A250">
         <v>249</v>
       </c>
@@ -7794,7 +7789,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7">
       <c r="A251">
         <v>250</v>
       </c>
@@ -7817,7 +7812,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7">
       <c r="A252">
         <v>251</v>
       </c>
@@ -7840,7 +7835,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7">
       <c r="A253">
         <v>252</v>
       </c>
@@ -7860,7 +7855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7">
       <c r="A254">
         <v>253</v>
       </c>
@@ -7883,7 +7878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7">
       <c r="A255">
         <v>254</v>
       </c>
@@ -7903,7 +7898,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7">
       <c r="A256">
         <v>255</v>
       </c>
@@ -7923,7 +7918,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7">
       <c r="A257">
         <v>256</v>
       </c>
@@ -7946,7 +7941,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7">
       <c r="A258">
         <v>257</v>
       </c>
@@ -7966,7 +7961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7">
       <c r="A259">
         <v>258</v>
       </c>
@@ -7986,7 +7981,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7">
       <c r="A260">
         <v>259</v>
       </c>
@@ -8009,7 +8004,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7">
       <c r="A261">
         <v>260</v>
       </c>
@@ -8032,7 +8027,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7">
       <c r="A262">
         <v>261</v>
       </c>
@@ -8055,7 +8050,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7">
       <c r="A263">
         <v>262</v>
       </c>
@@ -8075,7 +8070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7">
       <c r="A264">
         <v>263</v>
       </c>
@@ -8095,7 +8090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7">
       <c r="A265">
         <v>264</v>
       </c>
@@ -8115,7 +8110,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7">
       <c r="A266">
         <v>265</v>
       </c>
@@ -8135,7 +8130,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7">
       <c r="A267">
         <v>266</v>
       </c>
@@ -8155,7 +8150,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7">
       <c r="A268">
         <v>267</v>
       </c>
@@ -8175,7 +8170,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7">
       <c r="A269">
         <v>268</v>
       </c>
@@ -8195,7 +8190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7">
       <c r="A270">
         <v>269</v>
       </c>
@@ -8215,7 +8210,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7">
       <c r="A271">
         <v>270</v>
       </c>
@@ -8235,7 +8230,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7">
       <c r="A272">
         <v>271</v>
       </c>
@@ -8255,7 +8250,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6">
       <c r="A273">
         <v>272</v>
       </c>
@@ -8275,7 +8270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6">
       <c r="A274">
         <v>273</v>
       </c>
@@ -8295,7 +8290,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6">
       <c r="A275">
         <v>274</v>
       </c>
@@ -8315,7 +8310,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6">
       <c r="A276">
         <v>275</v>
       </c>
@@ -8335,7 +8330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6">
       <c r="A277">
         <v>276</v>
       </c>
@@ -8355,7 +8350,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6">
       <c r="A278">
         <v>277</v>
       </c>
@@ -8375,7 +8370,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6">
       <c r="A279">
         <v>278</v>
       </c>
@@ -8395,7 +8390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6">
       <c r="A280">
         <v>279</v>
       </c>
@@ -8415,7 +8410,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6">
       <c r="A281">
         <v>280</v>
       </c>
@@ -8435,7 +8430,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6">
       <c r="A282">
         <v>281</v>
       </c>
@@ -8455,7 +8450,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6">
       <c r="A283">
         <v>282</v>
       </c>
@@ -8475,7 +8470,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6">
       <c r="A284">
         <v>283</v>
       </c>
@@ -8495,7 +8490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6">
       <c r="A285">
         <v>284</v>
       </c>
@@ -8515,7 +8510,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6">
       <c r="A286">
         <v>285</v>
       </c>
@@ -8535,7 +8530,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6">
       <c r="A287">
         <v>286</v>
       </c>
@@ -8555,7 +8550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6">
       <c r="A288">
         <v>287</v>
       </c>
@@ -8575,7 +8570,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7">
       <c r="A289">
         <v>288</v>
       </c>
@@ -8595,7 +8590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7">
       <c r="A290">
         <v>289</v>
       </c>
@@ -8615,7 +8610,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7">
       <c r="A291">
         <v>290</v>
       </c>
@@ -8635,7 +8630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7">
       <c r="A292">
         <v>291</v>
       </c>
@@ -8655,7 +8650,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7">
       <c r="A293">
         <v>292</v>
       </c>
@@ -8675,7 +8670,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7">
       <c r="A294">
         <v>293</v>
       </c>
@@ -8695,7 +8690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7">
       <c r="A295">
         <v>294</v>
       </c>
@@ -8715,7 +8710,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7">
       <c r="A296">
         <v>295</v>
       </c>
@@ -8735,7 +8730,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7">
       <c r="A297">
         <v>296</v>
       </c>
@@ -8755,7 +8750,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7">
       <c r="A298">
         <v>297</v>
       </c>
@@ -8775,7 +8770,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7">
       <c r="A299">
         <v>298</v>
       </c>
@@ -8795,7 +8790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7">
       <c r="A300">
         <v>299</v>
       </c>
@@ -8815,7 +8810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7">
       <c r="A301">
         <v>300</v>
       </c>
@@ -8835,7 +8830,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7">
       <c r="A302">
         <v>301</v>
       </c>
@@ -8855,7 +8850,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7">
       <c r="A303">
         <v>302</v>
       </c>
@@ -8878,7 +8873,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7">
       <c r="A304">
         <v>303</v>
       </c>
@@ -8898,7 +8893,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7">
       <c r="A305">
         <v>304</v>
       </c>
@@ -8918,7 +8913,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7">
       <c r="A306">
         <v>305</v>
       </c>
@@ -8938,7 +8933,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7">
       <c r="A307">
         <v>306</v>
       </c>
@@ -8958,7 +8953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7">
       <c r="A308">
         <v>307</v>
       </c>
@@ -8978,7 +8973,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7">
       <c r="A309">
         <v>308</v>
       </c>
@@ -8998,7 +8993,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7">
       <c r="A310">
         <v>309</v>
       </c>
@@ -9018,7 +9013,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7">
       <c r="A311">
         <v>310</v>
       </c>
@@ -9041,7 +9036,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7">
       <c r="A312">
         <v>311</v>
       </c>
@@ -9064,7 +9059,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7">
       <c r="A313">
         <v>312</v>
       </c>
@@ -9087,7 +9082,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7">
       <c r="A314">
         <v>313</v>
       </c>
@@ -9110,7 +9105,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7">
       <c r="A315">
         <v>314</v>
       </c>
@@ -9130,7 +9125,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7">
       <c r="A316">
         <v>315</v>
       </c>
@@ -9150,7 +9145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7">
       <c r="A317">
         <v>316</v>
       </c>
@@ -9170,7 +9165,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7">
       <c r="A318">
         <v>317</v>
       </c>
@@ -9190,7 +9185,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7">
       <c r="A319">
         <v>318</v>
       </c>
@@ -9210,7 +9205,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7">
       <c r="A320">
         <v>319</v>
       </c>
@@ -9230,7 +9225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6">
       <c r="A321">
         <v>320</v>
       </c>
@@ -9250,7 +9245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6">
       <c r="A322">
         <v>321</v>
       </c>
@@ -9270,7 +9265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6">
       <c r="A323">
         <v>322</v>
       </c>
@@ -9290,7 +9285,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6">
       <c r="A324">
         <v>323</v>
       </c>
@@ -9310,7 +9305,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6">
       <c r="A325">
         <v>324</v>
       </c>
@@ -9330,7 +9325,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6">
       <c r="A326">
         <v>325</v>
       </c>
@@ -9350,7 +9345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6">
       <c r="A327">
         <v>326</v>
       </c>
@@ -9370,7 +9365,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6">
       <c r="A328">
         <v>327</v>
       </c>
@@ -9390,7 +9385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6">
       <c r="A329">
         <v>328</v>
       </c>
@@ -9410,7 +9405,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6">
       <c r="A330">
         <v>329</v>
       </c>
@@ -9430,7 +9425,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6">
       <c r="A331">
         <v>330</v>
       </c>
@@ -9450,7 +9445,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6">
       <c r="A332">
         <v>331</v>
       </c>
@@ -9470,7 +9465,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6">
       <c r="A333">
         <v>332</v>
       </c>
@@ -9490,7 +9485,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6">
       <c r="A334">
         <v>333</v>
       </c>
@@ -9510,7 +9505,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6">
       <c r="A335">
         <v>334</v>
       </c>
@@ -9530,7 +9525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6">
       <c r="A336">
         <v>335</v>
       </c>
@@ -9550,7 +9545,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7">
       <c r="A337">
         <v>336</v>
       </c>
@@ -9570,7 +9565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7">
       <c r="A338">
         <v>337</v>
       </c>
@@ -9590,7 +9585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7">
       <c r="A339">
         <v>338</v>
       </c>
@@ -9610,7 +9605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7">
       <c r="A340">
         <v>339</v>
       </c>
@@ -9630,7 +9625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7">
       <c r="A341">
         <v>340</v>
       </c>
@@ -9650,7 +9645,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7">
       <c r="A342">
         <v>341</v>
       </c>
@@ -9670,7 +9665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7">
       <c r="A343">
         <v>342</v>
       </c>
@@ -9693,7 +9688,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7">
       <c r="A344">
         <v>343</v>
       </c>
@@ -9713,7 +9708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7">
       <c r="A345">
         <v>344</v>
       </c>
@@ -9733,7 +9728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7">
       <c r="A346">
         <v>345</v>
       </c>
@@ -9753,7 +9748,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7">
       <c r="A347">
         <v>346</v>
       </c>
@@ -9776,7 +9771,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7">
       <c r="A348">
         <v>347</v>
       </c>
@@ -9796,7 +9791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7">
       <c r="A349">
         <v>348</v>
       </c>
@@ -9816,7 +9811,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7">
       <c r="A350">
         <v>349</v>
       </c>
@@ -9836,7 +9831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7">
       <c r="A351">
         <v>350</v>
       </c>
@@ -9859,7 +9854,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7">
       <c r="A352">
         <v>351</v>
       </c>
@@ -9879,7 +9874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7">
       <c r="A353">
         <v>352</v>
       </c>
@@ -9899,7 +9894,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7">
       <c r="A354">
         <v>353</v>
       </c>
@@ -9919,7 +9914,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7">
       <c r="A355">
         <v>354</v>
       </c>
@@ -9939,7 +9934,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7">
       <c r="A356">
         <v>355</v>
       </c>
@@ -9959,7 +9954,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7">
       <c r="A357">
         <v>356</v>
       </c>
@@ -9982,7 +9977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7">
       <c r="A358">
         <v>357</v>
       </c>
@@ -10002,7 +9997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7">
       <c r="A359">
         <v>358</v>
       </c>
@@ -10025,7 +10020,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7">
       <c r="A360">
         <v>359</v>
       </c>
@@ -10045,7 +10040,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7">
       <c r="A361">
         <v>360</v>
       </c>
@@ -10065,7 +10060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7">
       <c r="A362">
         <v>361</v>
       </c>
@@ -10085,7 +10080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7">
       <c r="A363">
         <v>362</v>
       </c>
@@ -10105,7 +10100,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7">
       <c r="A364">
         <v>363</v>
       </c>
@@ -10125,7 +10120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7">
       <c r="A365">
         <v>364</v>
       </c>
@@ -10145,7 +10140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7">
       <c r="A366">
         <v>365</v>
       </c>
@@ -10165,7 +10160,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7">
       <c r="A367">
         <v>366</v>
       </c>
@@ -10185,7 +10180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7">
       <c r="A368">
         <v>367</v>
       </c>
@@ -10208,7 +10203,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7">
       <c r="A369">
         <v>368</v>
       </c>
@@ -10228,7 +10223,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7">
       <c r="A370">
         <v>369</v>
       </c>
@@ -10248,7 +10243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7">
       <c r="A371">
         <v>370</v>
       </c>
@@ -10268,7 +10263,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7">
       <c r="A372">
         <v>371</v>
       </c>
@@ -10288,7 +10283,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7">
       <c r="A373">
         <v>372</v>
       </c>
@@ -10308,7 +10303,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7">
       <c r="A374">
         <v>373</v>
       </c>
@@ -10328,7 +10323,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7">
       <c r="A375">
         <v>374</v>
       </c>
@@ -10348,7 +10343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7">
       <c r="A376">
         <v>375</v>
       </c>
@@ -10371,7 +10366,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7">
       <c r="A377">
         <v>376</v>
       </c>
@@ -10391,7 +10386,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7">
       <c r="A378">
         <v>377</v>
       </c>
@@ -10411,7 +10406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7">
       <c r="A379">
         <v>378</v>
       </c>
@@ -10431,7 +10426,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7">
       <c r="A380">
         <v>379</v>
       </c>
@@ -10451,7 +10446,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7">
       <c r="A381">
         <v>380</v>
       </c>
@@ -10471,7 +10466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7">
       <c r="A382">
         <v>381</v>
       </c>
@@ -10494,7 +10489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7">
       <c r="A383">
         <v>382</v>
       </c>
@@ -10514,7 +10509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7">
       <c r="A384">
         <v>383</v>
       </c>
@@ -10534,7 +10529,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7">
       <c r="A385">
         <v>384</v>
       </c>
@@ -10557,7 +10552,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7">
       <c r="A386">
         <v>385</v>
       </c>
@@ -10577,7 +10572,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7">
       <c r="A387">
         <v>386</v>
       </c>
@@ -10597,7 +10592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7">
       <c r="A388">
         <v>387</v>
       </c>
@@ -10620,7 +10615,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7">
       <c r="A389">
         <v>388</v>
       </c>
@@ -10640,7 +10635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7">
       <c r="A390">
         <v>389</v>
       </c>
@@ -10660,7 +10655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7">
       <c r="A391">
         <v>390</v>
       </c>
@@ -10680,7 +10675,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7">
       <c r="A392">
         <v>391</v>
       </c>
@@ -10700,7 +10695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7">
       <c r="A393">
         <v>392</v>
       </c>
@@ -10720,7 +10715,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7">
       <c r="A394">
         <v>393</v>
       </c>
@@ -10740,7 +10735,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7">
       <c r="A395">
         <v>394</v>
       </c>
@@ -10763,7 +10758,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7">
       <c r="A396">
         <v>395</v>
       </c>
@@ -10783,7 +10778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7">
       <c r="A397">
         <v>396</v>
       </c>
@@ -10803,7 +10798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7">
       <c r="A398">
         <v>397</v>
       </c>
@@ -10823,7 +10818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7">
       <c r="A399">
         <v>398</v>
       </c>
@@ -10843,7 +10838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7">
       <c r="A400">
         <v>399</v>
       </c>
@@ -10863,7 +10858,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6">
       <c r="A401">
         <v>400</v>
       </c>
@@ -10883,7 +10878,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6">
       <c r="A402">
         <v>401</v>
       </c>
@@ -10903,7 +10898,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6">
       <c r="A403">
         <v>402</v>
       </c>
@@ -10923,7 +10918,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6">
       <c r="A404">
         <v>403</v>
       </c>
@@ -10943,7 +10938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6">
       <c r="A405">
         <v>404</v>
       </c>
@@ -10963,7 +10958,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6">
       <c r="A406">
         <v>405</v>
       </c>
@@ -10983,7 +10978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6">
       <c r="A407">
         <v>406</v>
       </c>
@@ -11003,7 +10998,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6">
       <c r="A408">
         <v>407</v>
       </c>
@@ -11023,7 +11018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6">
       <c r="A409">
         <v>408</v>
       </c>
@@ -11043,7 +11038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6">
       <c r="A410">
         <v>409</v>
       </c>
@@ -11063,7 +11058,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6">
       <c r="A411">
         <v>410</v>
       </c>
@@ -11083,7 +11078,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6">
       <c r="A412">
         <v>411</v>
       </c>
@@ -11103,7 +11098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6">
       <c r="A413">
         <v>412</v>
       </c>
@@ -11123,7 +11118,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6">
       <c r="A414">
         <v>413</v>
       </c>
@@ -11143,7 +11138,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6">
       <c r="A415">
         <v>414</v>
       </c>
@@ -11163,7 +11158,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6">
       <c r="A416">
         <v>415</v>
       </c>
@@ -11183,7 +11178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7">
       <c r="A417">
         <v>416</v>
       </c>
@@ -11203,7 +11198,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7">
       <c r="A418">
         <v>417</v>
       </c>
@@ -11223,7 +11218,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7">
       <c r="A419">
         <v>418</v>
       </c>
@@ -11243,7 +11238,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7">
       <c r="A420">
         <v>419</v>
       </c>
@@ -11263,7 +11258,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7">
       <c r="A421">
         <v>420</v>
       </c>
@@ -11286,7 +11281,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7">
       <c r="A422">
         <v>421</v>
       </c>
@@ -11309,7 +11304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7">
       <c r="A423">
         <v>422</v>
       </c>
@@ -11332,7 +11327,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7">
       <c r="A424">
         <v>423</v>
       </c>
@@ -11355,7 +11350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7">
       <c r="A425">
         <v>424</v>
       </c>
@@ -11378,7 +11373,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7">
       <c r="A426">
         <v>425</v>
       </c>
@@ -11401,7 +11396,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7">
       <c r="A427">
         <v>426</v>
       </c>
@@ -11424,7 +11419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7">
       <c r="A428">
         <v>427</v>
       </c>
@@ -11447,7 +11442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7">
       <c r="A429">
         <v>428</v>
       </c>
@@ -11470,7 +11465,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7">
       <c r="A430">
         <v>429</v>
       </c>
@@ -11493,7 +11488,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7">
       <c r="A431">
         <v>430</v>
       </c>
@@ -11516,7 +11511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7">
       <c r="A432">
         <v>431</v>
       </c>
@@ -11539,7 +11534,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7">
       <c r="A433">
         <v>432</v>
       </c>
@@ -11562,7 +11557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7">
       <c r="A434">
         <v>433</v>
       </c>
@@ -11585,7 +11580,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7">
       <c r="A435">
         <v>434</v>
       </c>
@@ -11608,7 +11603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7">
       <c r="A436">
         <v>435</v>
       </c>
@@ -11631,7 +11626,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7">
       <c r="A437">
         <v>436</v>
       </c>
@@ -11654,7 +11649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7">
       <c r="A438">
         <v>437</v>
       </c>
@@ -11677,7 +11672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7">
       <c r="A439">
         <v>438</v>
       </c>
@@ -11700,7 +11695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7">
       <c r="A440">
         <v>439</v>
       </c>
@@ -11723,7 +11718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7">
       <c r="A441">
         <v>440</v>
       </c>
@@ -11743,7 +11738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7">
       <c r="A442">
         <v>441</v>
       </c>
@@ -11766,7 +11761,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7">
       <c r="A443">
         <v>442</v>
       </c>
@@ -11789,7 +11784,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7">
       <c r="A444">
         <v>443</v>
       </c>
@@ -11812,7 +11807,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7">
       <c r="A445">
         <v>444</v>
       </c>
@@ -11835,7 +11830,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7">
       <c r="A446">
         <v>445</v>
       </c>
@@ -11858,7 +11853,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7">
       <c r="A447">
         <v>446</v>
       </c>
@@ -11881,7 +11876,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7">
       <c r="A448">
         <v>447</v>
       </c>
@@ -11904,7 +11899,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6">
       <c r="A449">
         <v>448</v>
       </c>
@@ -11924,7 +11919,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6">
       <c r="A450">
         <v>449</v>
       </c>
@@ -11944,7 +11939,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6">
       <c r="A451">
         <v>450</v>
       </c>
@@ -11964,7 +11959,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6">
       <c r="A452">
         <v>451</v>
       </c>
@@ -11984,7 +11979,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6">
       <c r="A453">
         <v>452</v>
       </c>
@@ -12004,7 +11999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6">
       <c r="A454">
         <v>453</v>
       </c>
@@ -12024,7 +12019,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6">
       <c r="A455">
         <v>454</v>
       </c>
@@ -12044,7 +12039,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6">
       <c r="A456">
         <v>455</v>
       </c>
@@ -12064,7 +12059,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6">
       <c r="A457">
         <v>456</v>
       </c>
@@ -12084,7 +12079,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6">
       <c r="A458">
         <v>457</v>
       </c>
@@ -12104,7 +12099,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6">
       <c r="A459">
         <v>458</v>
       </c>
@@ -12124,7 +12119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6">
       <c r="A460">
         <v>459</v>
       </c>
@@ -12144,7 +12139,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6">
       <c r="A461">
         <v>460</v>
       </c>
@@ -12164,7 +12159,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6">
       <c r="A462">
         <v>461</v>
       </c>
@@ -12184,7 +12179,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6">
       <c r="A463">
         <v>462</v>
       </c>
@@ -12204,7 +12199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6">
       <c r="A464">
         <v>463</v>
       </c>
@@ -12224,7 +12219,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6">
       <c r="A465">
         <v>464</v>
       </c>
@@ -12244,7 +12239,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6">
       <c r="A466">
         <v>465</v>
       </c>
@@ -12264,7 +12259,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6">
       <c r="A467">
         <v>466</v>
       </c>
@@ -12284,7 +12279,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6">
       <c r="A468">
         <v>467</v>
       </c>
@@ -12304,7 +12299,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6">
       <c r="A469">
         <v>468</v>
       </c>
@@ -12324,7 +12319,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6">
       <c r="A470">
         <v>469</v>
       </c>
@@ -12344,7 +12339,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6">
       <c r="A471">
         <v>470</v>
       </c>
@@ -12364,7 +12359,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6">
       <c r="A472">
         <v>471</v>
       </c>
@@ -12384,7 +12379,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6">
       <c r="A473">
         <v>472</v>
       </c>
@@ -12404,7 +12399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6">
       <c r="A474">
         <v>473</v>
       </c>
@@ -12424,7 +12419,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6">
       <c r="A475">
         <v>474</v>
       </c>
@@ -12444,7 +12439,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6">
       <c r="A476">
         <v>475</v>
       </c>
@@ -12464,7 +12459,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6">
       <c r="A477">
         <v>476</v>
       </c>
@@ -12484,7 +12479,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6">
       <c r="A478">
         <v>477</v>
       </c>
@@ -12504,7 +12499,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6">
       <c r="A479">
         <v>478</v>
       </c>
@@ -12524,7 +12519,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6">
       <c r="A480">
         <v>479</v>
       </c>
@@ -12544,7 +12539,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7">
       <c r="A481">
         <v>480</v>
       </c>
@@ -12564,7 +12559,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7">
       <c r="A482">
         <v>481</v>
       </c>
@@ -12584,7 +12579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7">
       <c r="A483">
         <v>482</v>
       </c>
@@ -12604,7 +12599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7">
       <c r="A484">
         <v>483</v>
       </c>
@@ -12624,7 +12619,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7">
       <c r="A485">
         <v>484</v>
       </c>
@@ -12644,7 +12639,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:7">
       <c r="A486">
         <v>485</v>
       </c>
@@ -12664,7 +12659,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:7">
       <c r="A487">
         <v>486</v>
       </c>
@@ -12684,7 +12679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:7">
       <c r="A488">
         <v>487</v>
       </c>
@@ -12704,7 +12699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7">
       <c r="A489">
         <v>488</v>
       </c>
@@ -12724,7 +12719,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:7">
       <c r="A490">
         <v>489</v>
       </c>
@@ -12744,7 +12739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:7">
       <c r="A491">
         <v>490</v>
       </c>
@@ -12764,7 +12759,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:7">
       <c r="A492">
         <v>491</v>
       </c>
@@ -12784,7 +12779,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7">
       <c r="A493">
         <v>492</v>
       </c>
@@ -12804,7 +12799,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:7">
       <c r="A494">
         <v>493</v>
       </c>
@@ -12827,7 +12822,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:7">
       <c r="A495">
         <v>494</v>
       </c>
@@ -12847,7 +12842,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:7">
       <c r="A496">
         <v>495</v>
       </c>
@@ -12867,7 +12862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7">
       <c r="A497">
         <v>496</v>
       </c>
@@ -12887,7 +12882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7">
       <c r="A498">
         <v>497</v>
       </c>
@@ -12907,7 +12902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7">
       <c r="A499">
         <v>498</v>
       </c>
@@ -12927,7 +12922,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:7">
       <c r="A500">
         <v>499</v>
       </c>
@@ -12947,7 +12942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7">
       <c r="A501">
         <v>500</v>
       </c>
@@ -12967,7 +12962,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7">
       <c r="A502">
         <v>501</v>
       </c>
@@ -12990,7 +12985,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:7">
       <c r="A503">
         <v>502</v>
       </c>
@@ -13013,7 +13008,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:7">
       <c r="A504">
         <v>503</v>
       </c>
@@ -13033,7 +13028,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7">
       <c r="A505">
         <v>504</v>
       </c>
@@ -13056,7 +13051,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:7">
       <c r="A506">
         <v>505</v>
       </c>
@@ -13076,7 +13071,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:7">
       <c r="A507">
         <v>506</v>
       </c>
@@ -13096,7 +13091,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:7">
       <c r="A508">
         <v>507</v>
       </c>
@@ -13116,7 +13111,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7">
       <c r="A509">
         <v>508</v>
       </c>
@@ -13139,7 +13134,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:7">
       <c r="A510">
         <v>509</v>
       </c>
@@ -13159,7 +13154,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:7">
       <c r="A511">
         <v>510</v>
       </c>
@@ -13179,7 +13174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:7">
       <c r="A512">
         <v>511</v>
       </c>
@@ -13199,7 +13194,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7">
       <c r="A513">
         <v>512</v>
       </c>
@@ -13219,7 +13214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:7">
       <c r="A514">
         <v>513</v>
       </c>
@@ -13239,7 +13234,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7">
       <c r="A515">
         <v>514</v>
       </c>
@@ -13259,7 +13254,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:7">
       <c r="A516">
         <v>515</v>
       </c>
@@ -13279,7 +13274,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7">
       <c r="A517">
         <v>516</v>
       </c>
@@ -13299,7 +13294,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7">
       <c r="A518">
         <v>517</v>
       </c>
@@ -13319,7 +13314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7">
       <c r="A519">
         <v>518</v>
       </c>
@@ -13342,7 +13337,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:7">
       <c r="A520">
         <v>519</v>
       </c>
@@ -13362,7 +13357,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7">
       <c r="A521">
         <v>520</v>
       </c>
@@ -13382,7 +13377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:7">
       <c r="A522">
         <v>521</v>
       </c>
@@ -13402,7 +13397,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7">
       <c r="A523">
         <v>522</v>
       </c>
@@ -13422,7 +13417,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:7">
       <c r="A524">
         <v>523</v>
       </c>
@@ -13442,7 +13437,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7">
       <c r="A525">
         <v>524</v>
       </c>
@@ -13462,7 +13457,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7">
       <c r="A526">
         <v>525</v>
       </c>
@@ -13482,7 +13477,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7">
       <c r="A527">
         <v>526</v>
       </c>
@@ -13502,7 +13497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:7">
       <c r="A528">
         <v>527</v>
       </c>
@@ -13522,7 +13517,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7">
       <c r="A529">
         <v>528</v>
       </c>
@@ -13542,7 +13537,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7">
       <c r="A530">
         <v>529</v>
       </c>
@@ -13562,7 +13557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7">
       <c r="A531">
         <v>530</v>
       </c>
@@ -13585,7 +13580,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:7">
       <c r="A532">
         <v>531</v>
       </c>
@@ -13605,7 +13600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7">
       <c r="A533">
         <v>532</v>
       </c>
@@ -13628,7 +13623,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:7">
       <c r="A534">
         <v>533</v>
       </c>
@@ -13648,7 +13643,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:7">
       <c r="A535">
         <v>534</v>
       </c>
@@ -13668,7 +13663,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:7">
       <c r="A536">
         <v>535</v>
       </c>
@@ -13688,7 +13683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:7">
       <c r="A537">
         <v>536</v>
       </c>
@@ -13708,7 +13703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:7">
       <c r="A538">
         <v>537</v>
       </c>
@@ -13728,7 +13723,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:7">
       <c r="A539">
         <v>538</v>
       </c>
@@ -13748,7 +13743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:7">
       <c r="A540">
         <v>539</v>
       </c>
@@ -13768,7 +13763,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:7">
       <c r="A541">
         <v>540</v>
       </c>
@@ -13788,7 +13783,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:7">
       <c r="A542">
         <v>541</v>
       </c>
@@ -13808,7 +13803,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:7">
       <c r="A543">
         <v>542</v>
       </c>
@@ -13828,7 +13823,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:7">
       <c r="A544">
         <v>543</v>
       </c>
@@ -13848,7 +13843,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:7">
       <c r="A545">
         <v>544</v>
       </c>
@@ -13868,7 +13863,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:7">
       <c r="A546">
         <v>545</v>
       </c>
@@ -13888,7 +13883,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:7">
       <c r="A547">
         <v>546</v>
       </c>
@@ -13908,7 +13903,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:7">
       <c r="A548">
         <v>547</v>
       </c>
@@ -13928,7 +13923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:7">
       <c r="A549">
         <v>548</v>
       </c>
@@ -13951,7 +13946,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:7">
       <c r="A550">
         <v>549</v>
       </c>
@@ -13974,7 +13969,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:7">
       <c r="A551">
         <v>550</v>
       </c>
@@ -13997,7 +13992,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:7">
       <c r="A552">
         <v>551</v>
       </c>
@@ -14017,7 +14012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:7">
       <c r="A553">
         <v>552</v>
       </c>
@@ -14040,7 +14035,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:7">
       <c r="A554">
         <v>553</v>
       </c>
@@ -14063,7 +14058,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:7">
       <c r="A555">
         <v>554</v>
       </c>
@@ -14083,7 +14078,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:7">
       <c r="A556">
         <v>555</v>
       </c>
@@ -14103,7 +14098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:7">
       <c r="A557">
         <v>556</v>
       </c>
@@ -14126,7 +14121,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:7">
       <c r="A558">
         <v>557</v>
       </c>
@@ -14146,7 +14141,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:7">
       <c r="A559">
         <v>558</v>
       </c>
@@ -14169,7 +14164,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:7">
       <c r="A560">
         <v>559</v>
       </c>
@@ -14192,7 +14187,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6">
       <c r="A561">
         <v>560</v>
       </c>
@@ -14212,7 +14207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6">
       <c r="A562">
         <v>561</v>
       </c>
@@ -14232,7 +14227,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6">
       <c r="A563">
         <v>562</v>
       </c>
@@ -14252,7 +14247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6">
       <c r="A564">
         <v>563</v>
       </c>
@@ -14272,7 +14267,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6">
       <c r="A565">
         <v>564</v>
       </c>
@@ -14292,7 +14287,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6">
       <c r="A566">
         <v>565</v>
       </c>
@@ -14312,7 +14307,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6">
       <c r="A567">
         <v>566</v>
       </c>
@@ -14332,7 +14327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6">
       <c r="A568">
         <v>567</v>
       </c>
@@ -14353,15 +14348,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G568" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G568"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
@@ -14371,7 +14366,7 @@
     <col min="6" max="6" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>556</v>
       </c>
@@ -14391,7 +14386,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -14411,7 +14406,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -14431,7 +14426,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -14451,7 +14446,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -14471,7 +14466,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -14491,7 +14486,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -14511,7 +14506,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -14531,7 +14526,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -14551,7 +14546,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -14571,7 +14566,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -14591,7 +14586,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -14611,7 +14606,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -14631,7 +14626,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -14651,7 +14646,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -14671,7 +14666,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -14691,7 +14686,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
@@ -14711,7 +14706,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
@@ -14731,7 +14726,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18</v>
       </c>
@@ -14751,7 +14746,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19</v>
       </c>
@@ -14771,7 +14766,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
@@ -14791,7 +14786,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>21</v>
       </c>
@@ -14811,7 +14806,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>22</v>
       </c>
@@ -14831,7 +14826,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>23</v>
       </c>
@@ -14851,7 +14846,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>24</v>
       </c>
@@ -14871,7 +14866,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>25</v>
       </c>
@@ -14891,7 +14886,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>26</v>
       </c>
@@ -14911,7 +14906,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>27</v>
       </c>
@@ -14931,7 +14926,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>28</v>
       </c>
@@ -14951,7 +14946,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>29</v>
       </c>
@@ -14971,7 +14966,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>30</v>
       </c>
@@ -14991,7 +14986,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>31</v>
       </c>
@@ -15011,7 +15006,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>32</v>
       </c>
@@ -15031,7 +15026,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>33</v>
       </c>
@@ -15051,7 +15046,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>34</v>
       </c>
@@ -15071,7 +15066,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>35</v>
       </c>
@@ -15091,7 +15086,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>36</v>
       </c>
@@ -15111,7 +15106,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>37</v>
       </c>
@@ -15132,22 +15127,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F38" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:F38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15161,7 +15156,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>4</v>
       </c>
@@ -15175,7 +15170,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>8</v>
       </c>
@@ -15189,7 +15184,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>9</v>
       </c>
@@ -15203,7 +15198,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>14</v>
       </c>
@@ -15217,7 +15212,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>15</v>
       </c>
@@ -15231,7 +15226,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>16</v>
       </c>
@@ -15245,7 +15240,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>17</v>
       </c>
@@ -15259,7 +15254,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>18</v>
       </c>
@@ -15273,7 +15268,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>19</v>
       </c>
@@ -15287,7 +15282,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>20</v>
       </c>
@@ -15301,7 +15296,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>21</v>
       </c>
@@ -15315,7 +15310,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>22</v>
       </c>
@@ -15329,7 +15324,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>24</v>
       </c>
@@ -15343,7 +15338,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>28</v>
       </c>
@@ -15357,7 +15352,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>29</v>
       </c>
@@ -15371,7 +15366,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>30</v>
       </c>
@@ -15385,7 +15380,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>33</v>
       </c>
@@ -15399,7 +15394,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>40</v>
       </c>
@@ -15413,7 +15408,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>44</v>
       </c>
@@ -15427,7 +15422,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>69</v>
       </c>
@@ -15441,7 +15436,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>70</v>
       </c>
@@ -15455,7 +15450,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>71</v>
       </c>
@@ -15469,7 +15464,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>72</v>
       </c>
@@ -15483,7 +15478,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>73</v>
       </c>
@@ -15497,7 +15492,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>74</v>
       </c>
@@ -15511,7 +15506,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>75</v>
       </c>
@@ -15525,7 +15520,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>76</v>
       </c>
@@ -15539,7 +15534,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>77</v>
       </c>
@@ -15553,7 +15548,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>112</v>
       </c>
@@ -15567,7 +15562,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>115</v>
       </c>
@@ -15581,7 +15576,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>116</v>
       </c>
@@ -15595,7 +15590,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>117</v>
       </c>
@@ -15609,7 +15604,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>118</v>
       </c>
@@ -15623,7 +15618,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>119</v>
       </c>
@@ -15637,7 +15632,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>120</v>
       </c>
@@ -15651,7 +15646,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>121</v>
       </c>
@@ -15665,7 +15660,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>122</v>
       </c>
@@ -15679,7 +15674,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>123</v>
       </c>
@@ -15693,7 +15688,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>124</v>
       </c>
@@ -15707,7 +15702,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>125</v>
       </c>
@@ -15721,7 +15716,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>126</v>
       </c>
@@ -15735,7 +15730,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>127</v>
       </c>
@@ -15749,7 +15744,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>128</v>
       </c>
@@ -15763,7 +15758,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>129</v>
       </c>
@@ -15777,7 +15772,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>135</v>
       </c>
@@ -15791,7 +15786,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>136</v>
       </c>
@@ -15805,7 +15800,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>137</v>
       </c>
@@ -15819,7 +15814,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4">
       <c r="A49">
         <v>147</v>
       </c>
@@ -15833,7 +15828,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4">
       <c r="A50">
         <v>165</v>
       </c>
@@ -15847,7 +15842,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4">
       <c r="A51">
         <v>192</v>
       </c>
@@ -15861,7 +15856,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4">
       <c r="A52">
         <v>197</v>
       </c>
@@ -15875,7 +15870,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4">
       <c r="A53">
         <v>199</v>
       </c>
@@ -15889,7 +15884,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4">
       <c r="A54">
         <v>200</v>
       </c>
@@ -15903,7 +15898,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4">
       <c r="A55">
         <v>201</v>
       </c>
@@ -15917,7 +15912,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4">
       <c r="A56">
         <v>202</v>
       </c>
@@ -15931,7 +15926,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4">
       <c r="A57">
         <v>204</v>
       </c>
@@ -15945,7 +15940,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4">
       <c r="A58">
         <v>205</v>
       </c>
@@ -15959,7 +15954,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4">
       <c r="A59">
         <v>216</v>
       </c>
@@ -15973,7 +15968,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4">
       <c r="A60">
         <v>217</v>
       </c>
@@ -15987,7 +15982,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4">
       <c r="A61">
         <v>219</v>
       </c>
@@ -16001,7 +15996,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4">
       <c r="A62">
         <v>220</v>
       </c>
@@ -16015,7 +16010,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4">
       <c r="A63">
         <v>221</v>
       </c>
@@ -16029,7 +16024,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4">
       <c r="A64">
         <v>229</v>
       </c>
@@ -16043,7 +16038,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4">
       <c r="A65">
         <v>231</v>
       </c>
@@ -16057,7 +16052,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4">
       <c r="A66">
         <v>232</v>
       </c>
@@ -16071,7 +16066,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4">
       <c r="A67">
         <v>243</v>
       </c>
@@ -16085,7 +16080,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4">
       <c r="A68">
         <v>244</v>
       </c>
@@ -16099,7 +16094,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4">
       <c r="A69">
         <v>246</v>
       </c>
@@ -16113,7 +16108,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4">
       <c r="A70">
         <v>247</v>
       </c>
@@ -16127,7 +16122,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4">
       <c r="A71">
         <v>248</v>
       </c>
@@ -16141,7 +16136,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4">
       <c r="A72">
         <v>249</v>
       </c>
@@ -16155,7 +16150,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4">
       <c r="A73">
         <v>250</v>
       </c>
@@ -16169,7 +16164,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4">
       <c r="A74">
         <v>251</v>
       </c>
@@ -16183,7 +16178,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4">
       <c r="A75">
         <v>253</v>
       </c>
@@ -16197,7 +16192,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4">
       <c r="A76">
         <v>256</v>
       </c>
@@ -16211,7 +16206,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4">
       <c r="A77">
         <v>259</v>
       </c>
@@ -16225,7 +16220,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4">
       <c r="A78">
         <v>260</v>
       </c>
@@ -16239,7 +16234,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4">
       <c r="A79">
         <v>261</v>
       </c>
@@ -16253,7 +16248,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4">
       <c r="A80">
         <v>302</v>
       </c>
@@ -16267,7 +16262,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4">
       <c r="A81">
         <v>310</v>
       </c>
@@ -16281,7 +16276,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4">
       <c r="A82">
         <v>311</v>
       </c>
@@ -16295,7 +16290,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4">
       <c r="A83">
         <v>312</v>
       </c>
@@ -16309,7 +16304,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4">
       <c r="A84">
         <v>313</v>
       </c>
@@ -16323,7 +16318,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4">
       <c r="A85">
         <v>342</v>
       </c>
@@ -16337,7 +16332,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4">
       <c r="A86">
         <v>346</v>
       </c>
@@ -16351,7 +16346,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4">
       <c r="A87">
         <v>350</v>
       </c>
@@ -16365,7 +16360,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4">
       <c r="A88">
         <v>356</v>
       </c>
@@ -16379,7 +16374,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4">
       <c r="A89">
         <v>358</v>
       </c>
@@ -16393,7 +16388,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4">
       <c r="A90">
         <v>367</v>
       </c>
@@ -16407,7 +16402,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4">
       <c r="A91">
         <v>375</v>
       </c>
@@ -16421,7 +16416,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4">
       <c r="A92">
         <v>381</v>
       </c>
@@ -16435,7 +16430,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4">
       <c r="A93">
         <v>384</v>
       </c>
@@ -16449,7 +16444,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4">
       <c r="A94">
         <v>387</v>
       </c>
@@ -16463,7 +16458,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4">
       <c r="A95">
         <v>394</v>
       </c>
@@ -16477,7 +16472,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4">
       <c r="A96">
         <v>420</v>
       </c>
@@ -16491,7 +16486,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4">
       <c r="A97">
         <v>421</v>
       </c>
@@ -16505,7 +16500,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4">
       <c r="A98">
         <v>422</v>
       </c>
@@ -16519,7 +16514,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4">
       <c r="A99">
         <v>423</v>
       </c>
@@ -16533,7 +16528,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4">
       <c r="A100">
         <v>424</v>
       </c>
@@ -16547,7 +16542,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4">
       <c r="A101">
         <v>425</v>
       </c>
@@ -16561,7 +16556,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4">
       <c r="A102">
         <v>426</v>
       </c>
@@ -16575,7 +16570,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4">
       <c r="A103">
         <v>427</v>
       </c>
@@ -16589,7 +16584,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4">
       <c r="A104">
         <v>428</v>
       </c>
@@ -16603,7 +16598,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4">
       <c r="A105">
         <v>429</v>
       </c>
@@ -16617,7 +16612,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4">
       <c r="A106">
         <v>430</v>
       </c>
@@ -16631,7 +16626,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4">
       <c r="A107">
         <v>431</v>
       </c>
@@ -16645,7 +16640,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4">
       <c r="A108">
         <v>432</v>
       </c>
@@ -16659,7 +16654,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4">
       <c r="A109">
         <v>433</v>
       </c>
@@ -16673,7 +16668,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4">
       <c r="A110">
         <v>434</v>
       </c>
@@ -16687,7 +16682,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4">
       <c r="A111">
         <v>435</v>
       </c>
@@ -16701,7 +16696,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4">
       <c r="A112">
         <v>436</v>
       </c>
@@ -16715,7 +16710,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4">
       <c r="A113">
         <v>437</v>
       </c>
@@ -16729,7 +16724,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4">
       <c r="A114">
         <v>438</v>
       </c>
@@ -16743,7 +16738,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4">
       <c r="A115">
         <v>439</v>
       </c>
@@ -16757,7 +16752,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4">
       <c r="A116">
         <v>441</v>
       </c>
@@ -16771,7 +16766,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4">
       <c r="A117">
         <v>442</v>
       </c>
@@ -16785,7 +16780,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4">
       <c r="A118">
         <v>443</v>
       </c>
@@ -16799,7 +16794,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4">
       <c r="A119">
         <v>444</v>
       </c>
@@ -16813,7 +16808,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4">
       <c r="A120">
         <v>445</v>
       </c>
@@ -16827,7 +16822,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4">
       <c r="A121">
         <v>446</v>
       </c>
@@ -16841,7 +16836,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4">
       <c r="A122">
         <v>447</v>
       </c>
@@ -16855,7 +16850,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4">
       <c r="A123">
         <v>493</v>
       </c>
@@ -16869,7 +16864,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4">
       <c r="A124">
         <v>501</v>
       </c>
@@ -16883,7 +16878,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4">
       <c r="A125">
         <v>502</v>
       </c>
@@ -16897,7 +16892,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4">
       <c r="A126">
         <v>504</v>
       </c>
@@ -16911,7 +16906,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4">
       <c r="A127">
         <v>508</v>
       </c>
@@ -16925,7 +16920,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4">
       <c r="A128">
         <v>518</v>
       </c>
@@ -16939,7 +16934,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4">
       <c r="A129">
         <v>530</v>
       </c>
@@ -16953,7 +16948,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4">
       <c r="A130">
         <v>532</v>
       </c>
@@ -16967,7 +16962,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4">
       <c r="A131">
         <v>548</v>
       </c>
@@ -16981,7 +16976,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4">
       <c r="A132">
         <v>549</v>
       </c>
@@ -16995,7 +16990,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4">
       <c r="A133">
         <v>550</v>
       </c>
@@ -17009,7 +17004,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4">
       <c r="A134">
         <v>552</v>
       </c>
@@ -17023,7 +17018,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4">
       <c r="A135">
         <v>553</v>
       </c>
@@ -17037,7 +17032,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4">
       <c r="A136">
         <v>556</v>
       </c>
@@ -17051,7 +17046,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4">
       <c r="A137">
         <v>558</v>
       </c>
@@ -17065,7 +17060,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4">
       <c r="A138">
         <v>559</v>
       </c>
@@ -17080,22 +17075,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D138" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:D138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>605</v>
       </c>
@@ -17106,7 +17101,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -17117,7 +17112,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -17128,7 +17123,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -17139,7 +17134,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -17150,7 +17145,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -17161,7 +17156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -17172,7 +17167,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -17183,7 +17178,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -17194,7 +17189,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -17205,7 +17200,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -17216,7 +17211,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -17227,7 +17222,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -17238,7 +17233,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -17249,7 +17244,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -17260,7 +17255,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -17271,7 +17266,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -17282,7 +17277,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -17293,7 +17288,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -17304,7 +17299,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -17316,15 +17311,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C20" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:C20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -17339,7 +17334,7 @@
     <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>608</v>
       </c>
@@ -17375,21 +17370,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>615</v>
       </c>
@@ -17397,7 +17392,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>617</v>
       </c>
@@ -17405,7 +17400,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>566</v>
       </c>
@@ -17413,7 +17408,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -17421,7 +17416,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>621</v>
       </c>
@@ -17429,7 +17424,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>623</v>
       </c>
@@ -17437,7 +17432,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>625</v>
       </c>
@@ -17446,15 +17441,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B7" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED0AB500-8F71-4539-BB2D-EBFB6D4E037A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
     <col min="2" max="2" width="37.85546875" customWidth="1"/>
@@ -17463,7 +17458,7 @@
     <col min="5" max="5" width="33.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>645</v>
       </c>
@@ -17480,7 +17475,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15" customHeight="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -17497,7 +17492,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15" customHeight="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -17514,7 +17509,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15" customHeight="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -17531,7 +17526,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15" customHeight="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -17548,7 +17543,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15" customHeight="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -17565,7 +17560,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15" customHeight="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -17582,7 +17577,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="15" customHeight="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -17599,7 +17594,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="15" customHeight="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -17616,7 +17611,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15" customHeight="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -17633,7 +17628,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="15" customHeight="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -17650,7 +17645,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="15" customHeight="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -17667,7 +17662,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="15" customHeight="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -17684,7 +17679,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15" customHeight="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -17701,7 +17696,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15" customHeight="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -17718,7 +17713,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="15" customHeight="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -17735,7 +17730,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15" customHeight="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -17752,7 +17747,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="15" customHeight="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -17769,7 +17764,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="15" customHeight="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -17786,7 +17781,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="15" customHeight="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -17803,7 +17798,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="15" customHeight="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -17820,7 +17815,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="15" customHeight="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -17837,7 +17832,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="15" customHeight="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -17854,7 +17849,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="15" customHeight="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -17871,7 +17866,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="15" customHeight="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -17888,7 +17883,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="15" customHeight="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -17905,7 +17900,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="15" customHeight="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -17922,7 +17917,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="15" customHeight="1">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -17939,7 +17934,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="15" customHeight="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -17956,7 +17951,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="15" customHeight="1">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -17973,7 +17968,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="15" customHeight="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -17990,7 +17985,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="15" customHeight="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -18007,7 +18002,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="15" customHeight="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -18024,7 +18019,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="15" customHeight="1">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -18041,7 +18036,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="15" customHeight="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -18058,7 +18053,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="15" customHeight="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -18075,7 +18070,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15" customHeight="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -18092,7 +18087,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="15" customHeight="1">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -18109,7 +18104,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="15" customHeight="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -18126,7 +18121,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="15" customHeight="1">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -18143,7 +18138,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="15" customHeight="1">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -18160,7 +18155,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -18177,7 +18172,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="15" customHeight="1">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -18194,7 +18189,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="15" customHeight="1">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -18211,7 +18206,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="15" customHeight="1">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -18228,7 +18223,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="15" customHeight="1">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -18245,7 +18240,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="15" customHeight="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -18262,7 +18257,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="15" customHeight="1">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -18279,7 +18274,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="15" customHeight="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -18296,7 +18291,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="15" customHeight="1">
       <c r="A50" s="4">
         <v>49</v>
       </c>

--- a/pantallas_android/catalogo_parametros_del_mantenimiento_hvac_actualizado.xlsx
+++ b/pantallas_android/catalogo_parametros_del_mantenimiento_hvac_actualizado.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="692" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,8 @@
     <sheet name="ValoresEquipo" sheetId="5" r:id="rId5"/>
     <sheet name="Modelo_DDD" sheetId="6" r:id="rId6"/>
     <sheet name="Categorias" sheetId="8" r:id="rId7"/>
+    <sheet name="TipoEquipos" sheetId="9" r:id="rId8"/>
+    <sheet name="rack" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Actividad_Parametro!$A$1:$D$138</definedName>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3715" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3896" uniqueCount="824">
   <si>
     <t>IdActividad</t>
   </si>
@@ -2191,13 +2193,404 @@
   </si>
   <si>
     <t>Estación de transferencia</t>
+  </si>
+  <si>
+    <t>Ventilador / Blower / Turbinas</t>
+  </si>
+  <si>
+    <t>Válvula Termostática TXV</t>
+  </si>
+  <si>
+    <t>Válvula Electrónica EEV</t>
+  </si>
+  <si>
+    <t>Motor de Oscilacion (Louver)</t>
+  </si>
+  <si>
+    <t>Tarjeta de control (PCB)</t>
+  </si>
+  <si>
+    <t>Capacitor de arranque</t>
+  </si>
+  <si>
+    <t>Cajas de Selección de Modo (BS Box)</t>
+  </si>
+  <si>
+    <t>Tarjeta principal de comunicación RS-485</t>
+  </si>
+  <si>
+    <t>Sepertin Condensador</t>
+  </si>
+  <si>
+    <t>Sepertin Evaporador</t>
+  </si>
+  <si>
+    <t>Sistemas VRF / VRV (Flujo de Refrigerante Variable)</t>
+  </si>
+  <si>
+    <t>Tarjeta inteligente local</t>
+  </si>
+  <si>
+    <t>Bomba de condensado integrada</t>
+  </si>
+  <si>
+    <t>Tarjeta Transmisora</t>
+  </si>
+  <si>
+    <t>Drenaje / Bandeja / Dampers</t>
+  </si>
+  <si>
+    <t>Compresor de Alta Potencia Chiller</t>
+  </si>
+  <si>
+    <t>Unidades Scroll</t>
+  </si>
+  <si>
+    <t>Screw (Tornillo) o Centrífugas</t>
+  </si>
+  <si>
+    <t>Evaporador (Intercambiador)</t>
+  </si>
+  <si>
+    <t>Tipo de Equipos</t>
+  </si>
+  <si>
+    <t>Cassette Expansion Directa</t>
+  </si>
+  <si>
+    <t>Minisplit Expansion Directa</t>
+  </si>
+  <si>
+    <t>Piso-Techo Expansion Directa</t>
+  </si>
+  <si>
+    <t>Paquete / Rooftop Expansion Directa</t>
+  </si>
+  <si>
+    <t>Chiller enfriado por Aire</t>
+  </si>
+  <si>
+    <t>Chiller enfriado por Agua</t>
+  </si>
+  <si>
+    <t>Panel de Control Central (PLC, DDC o Termostato Inteligente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tablero de Control DDC </t>
+  </si>
+  <si>
+    <t>Direct Digital Control</t>
+  </si>
+  <si>
+    <t>Sensor de Temperatura</t>
+  </si>
+  <si>
+    <t>Sensor de Humedad</t>
+  </si>
+  <si>
+    <t>Torre de enfriamiento cerrada</t>
+  </si>
+  <si>
+    <t>Torre de enfriamiento abierta</t>
+  </si>
+  <si>
+    <t>Cuarto Frio</t>
+  </si>
+  <si>
+    <t>Vitrina</t>
+  </si>
+  <si>
+    <t>Rack de Compresores</t>
+  </si>
+  <si>
+    <t>EsMedible</t>
+  </si>
+  <si>
+    <t>Corriente consumida (Fase L1, L2, L3)</t>
+  </si>
+  <si>
+    <t>Valor nominal / máximo</t>
+  </si>
+  <si>
+    <t>Placa del fabricante</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>Tensión de alimentación</t>
+  </si>
+  <si>
+    <t>Valor nominal ($\pm 10\%$)</t>
+  </si>
+  <si>
+    <t>Placa del fabricante / Norma</t>
+  </si>
+  <si>
+    <t>Temperatura de descarga</t>
+  </si>
+  <si>
+    <t>Rango de operación</t>
+  </si>
+  <si>
+    <t>Manual del fabricante</t>
+  </si>
+  <si>
+    <t>Nivel de aceite en cárter</t>
+  </si>
+  <si>
+    <t>Nivel</t>
+  </si>
+  <si>
+    <t>% / Mirilla</t>
+  </si>
+  <si>
+    <t>Valor de referencia</t>
+  </si>
+  <si>
+    <t>Mirilla (1/2 a 3/4)</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>Resistencia de aislamiento del motor</t>
+  </si>
+  <si>
+    <t>Resistencia</t>
+  </si>
+  <si>
+    <t>M$\Omega$</t>
+  </si>
+  <si>
+    <t>Valor mínimo</t>
+  </si>
+  <si>
+    <t>Norma IEEE / Fabricante</t>
+  </si>
+  <si>
+    <t>Descripción en el Modelo</t>
+  </si>
+  <si>
+    <t>Compresor #1 / #2 / #N</t>
+  </si>
+  <si>
+    <t>Cada una de las etapas o unidades de compresión del Rack.</t>
+  </si>
+  <si>
+    <t>Controlador Central / PLC</t>
+  </si>
+  <si>
+    <t>Microprocesador que gestiona la secuencia de arranque y presiones.</t>
+  </si>
+  <si>
+    <t>SistemaAceite</t>
+  </si>
+  <si>
+    <t>Separador y Depósito de Aceite</t>
+  </si>
+  <si>
+    <t>Mantiene el nivel de lubricante en todos los compresores conectados.</t>
+  </si>
+  <si>
+    <t>Colector</t>
+  </si>
+  <si>
+    <t>Colector de Succión y Descarga</t>
+  </si>
+  <si>
+    <t>Protección</t>
+  </si>
+  <si>
+    <t>Presostatos y Válvulas de Seguridad</t>
+  </si>
+  <si>
+    <t>Dispositivos mecánicos y eléctricos de corte por presión/temperatura.</t>
+  </si>
+  <si>
+    <t>Tuberías principales (Headers) de baja y alta presión.</t>
+  </si>
+  <si>
+    <t>2. Parámetros Técnicos a Medir por Componente</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A. Por cada Compresor (Componente: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>Compresor #N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">B. Para el Colector Central (Componente: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>Colector de Succión y Descarga</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Presión de succión del Rack</t>
+  </si>
+  <si>
+    <t>Rango de Setpoint</t>
+  </si>
+  <si>
+    <t>Configuración del PLC</t>
+  </si>
+  <si>
+    <t>Presión de descarga del Rack</t>
+  </si>
+  <si>
+    <t>Superheat (Sobrecalentamiento) de succión</t>
+  </si>
+  <si>
+    <t>K / °C</t>
+  </si>
+  <si>
+    <t>Diseño del proyecto (8-12 K)</t>
+  </si>
+  <si>
+    <t>Subcooling (Subenfriamiento) de líquido</t>
+  </si>
+  <si>
+    <t>Diseño del proyecto</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C. Para el Sistema de Aceite y Control (Componentes: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>SistemaAceite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controlador</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Presión diferencial de aceite</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <t>Manual de la bomba de aceite</t>
+  </si>
+  <si>
+    <t>Nivel del depósito general de aceite</t>
+  </si>
+  <si>
+    <t>Valor nominal</t>
+  </si>
+  <si>
+    <t>Mirilla visual</t>
+  </si>
+  <si>
+    <t>Tensión de control (24VDC / 110VAC)</t>
+  </si>
+  <si>
+    <t>Diagrama eléctrico del tablero</t>
+  </si>
+  <si>
+    <t>Unidad Evaporadora</t>
+  </si>
+  <si>
+    <t>cámara frigorífica</t>
+  </si>
+  <si>
+    <t>Camara de Conservacion</t>
+  </si>
+  <si>
+    <t>Camara de Congelacion</t>
+  </si>
+  <si>
+    <t>Unidad de Ventilacion</t>
+  </si>
+  <si>
+    <t>Campana Extractora</t>
+  </si>
+  <si>
+    <t>ventilacion</t>
+  </si>
+  <si>
+    <t>Cortina de Aire</t>
+  </si>
+  <si>
+    <t>Caja de Volumen Variable (VAV o CVV)</t>
+  </si>
+  <si>
+    <t>Dispensador de Agua</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2217,6 +2610,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2244,7 +2643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2259,6 +2658,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17082,12 +17482,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="3" max="3" width="63.5703125" customWidth="1"/>
+    <col min="4" max="4" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17186,7 +17587,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -17263,10 +17664,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -17277,7 +17678,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -17288,7 +17689,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -17299,7 +17700,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -17308,6 +17709,126 @@
       </c>
       <c r="C20" t="s">
         <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="C23" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="C24" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="C25" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="C26" t="s">
+        <v>723</v>
+      </c>
+      <c r="D26" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="C27" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="C28" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="C29" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="C30" t="s">
+        <v>727</v>
+      </c>
+      <c r="D30" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="C31" t="s">
+        <v>728</v>
+      </c>
+      <c r="D31" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="C32" t="s">
+        <v>732</v>
+      </c>
+      <c r="D32" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" t="s">
+        <v>733</v>
+      </c>
+      <c r="D33" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34" t="s">
+        <v>734</v>
+      </c>
+      <c r="D34" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35" t="s">
+        <v>737</v>
+      </c>
+      <c r="D35" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4">
+      <c r="C36" t="s">
+        <v>738</v>
+      </c>
+      <c r="D36" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4">
+      <c r="C37" t="s">
+        <v>739</v>
+      </c>
+      <c r="D37" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4">
+      <c r="C38" t="s">
+        <v>747</v>
+      </c>
+      <c r="D38" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4">
+      <c r="C40" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4">
+      <c r="C41" t="s">
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -18311,4 +18832,617 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="55.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2" ht="15" customHeight="1">
+      <c r="B1" s="6" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2" ht="15" customHeight="1">
+      <c r="B2" s="3" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="15" customHeight="1">
+      <c r="B3" s="3" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="15" customHeight="1">
+      <c r="B4" s="3" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="15" customHeight="1">
+      <c r="B5" s="3" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="15" customHeight="1">
+      <c r="B6" s="3" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="15" customHeight="1">
+      <c r="B7" s="3" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="15" customHeight="1">
+      <c r="B8" s="3" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="15" customHeight="1">
+      <c r="B9" s="3" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="15" customHeight="1">
+      <c r="B10" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="15" customHeight="1">
+      <c r="B11" s="3" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="15" customHeight="1">
+      <c r="B12" s="3" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" ht="15" customHeight="1">
+      <c r="B13" s="3" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" ht="15" customHeight="1">
+      <c r="B14" s="3" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" ht="15" customHeight="1">
+      <c r="B15" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" ht="15" customHeight="1">
+      <c r="B16" s="3" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="15" customHeight="1">
+      <c r="B17" s="3" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="15" customHeight="1">
+      <c r="B18" s="3" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="15" customHeight="1">
+      <c r="B19" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="15" customHeight="1">
+      <c r="B20" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C20" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="15" customHeight="1">
+      <c r="B21" s="3" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="15" customHeight="1">
+      <c r="B22" s="3" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="15" customHeight="1">
+      <c r="B23" s="3" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15" customHeight="1">
+      <c r="B24" s="3" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="15" customHeight="1">
+      <c r="B25" s="3" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="15" customHeight="1">
+      <c r="B26" s="3" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="15" customHeight="1">
+      <c r="B27" s="3" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="15" customHeight="1">
+      <c r="B28" s="3" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="15" customHeight="1">
+      <c r="B29" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="C29" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" ht="15" customHeight="1">
+      <c r="B30" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="C30" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="15" customHeight="1">
+      <c r="B31" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="C31" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="15" customHeight="1">
+      <c r="B32" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="15" customHeight="1">
+      <c r="B33" t="s">
+        <v>819</v>
+      </c>
+      <c r="C33" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="15" customHeight="1">
+      <c r="B34" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="15" customHeight="1">
+      <c r="B35" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="15" customHeight="1">
+      <c r="B36" t="s">
+        <v>823</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>780</v>
+      </c>
+      <c r="C2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B3" t="s">
+        <v>782</v>
+      </c>
+      <c r="C3" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>784</v>
+      </c>
+      <c r="B4" t="s">
+        <v>785</v>
+      </c>
+      <c r="C4" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>787</v>
+      </c>
+      <c r="B5" t="s">
+        <v>788</v>
+      </c>
+      <c r="C5" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>789</v>
+      </c>
+      <c r="B6" t="s">
+        <v>790</v>
+      </c>
+      <c r="C6" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75">
+      <c r="A10" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>758</v>
+      </c>
+      <c r="B12" t="s">
+        <v>562</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>759</v>
+      </c>
+      <c r="E12" t="s">
+        <v>760</v>
+      </c>
+      <c r="F12" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>762</v>
+      </c>
+      <c r="B13" t="s">
+        <v>574</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>763</v>
+      </c>
+      <c r="E13" t="s">
+        <v>764</v>
+      </c>
+      <c r="F13" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>765</v>
+      </c>
+      <c r="B14" t="s">
+        <v>572</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>766</v>
+      </c>
+      <c r="E14" t="s">
+        <v>767</v>
+      </c>
+      <c r="F14" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>768</v>
+      </c>
+      <c r="B15" t="s">
+        <v>769</v>
+      </c>
+      <c r="C15" t="s">
+        <v>770</v>
+      </c>
+      <c r="D15" t="s">
+        <v>771</v>
+      </c>
+      <c r="E15" t="s">
+        <v>772</v>
+      </c>
+      <c r="F15" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>774</v>
+      </c>
+      <c r="B16" t="s">
+        <v>775</v>
+      </c>
+      <c r="C16" t="s">
+        <v>776</v>
+      </c>
+      <c r="D16" t="s">
+        <v>777</v>
+      </c>
+      <c r="E16" t="s">
+        <v>778</v>
+      </c>
+      <c r="F16" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75">
+      <c r="A18" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>796</v>
+      </c>
+      <c r="B20" t="s">
+        <v>570</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>797</v>
+      </c>
+      <c r="E20" t="s">
+        <v>798</v>
+      </c>
+      <c r="F20" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>799</v>
+      </c>
+      <c r="B21" t="s">
+        <v>570</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>797</v>
+      </c>
+      <c r="E21" t="s">
+        <v>798</v>
+      </c>
+      <c r="F21" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>800</v>
+      </c>
+      <c r="B22" t="s">
+        <v>572</v>
+      </c>
+      <c r="C22" t="s">
+        <v>801</v>
+      </c>
+      <c r="D22" t="s">
+        <v>766</v>
+      </c>
+      <c r="E22" t="s">
+        <v>802</v>
+      </c>
+      <c r="F22" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>803</v>
+      </c>
+      <c r="B23" t="s">
+        <v>572</v>
+      </c>
+      <c r="C23" t="s">
+        <v>801</v>
+      </c>
+      <c r="D23" t="s">
+        <v>766</v>
+      </c>
+      <c r="E23" t="s">
+        <v>804</v>
+      </c>
+      <c r="F23" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75">
+      <c r="A25" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>806</v>
+      </c>
+      <c r="B27" t="s">
+        <v>570</v>
+      </c>
+      <c r="C27" t="s">
+        <v>807</v>
+      </c>
+      <c r="D27" t="s">
+        <v>766</v>
+      </c>
+      <c r="E27" t="s">
+        <v>808</v>
+      </c>
+      <c r="F27" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>809</v>
+      </c>
+      <c r="B28" t="s">
+        <v>769</v>
+      </c>
+      <c r="C28" t="s">
+        <v>770</v>
+      </c>
+      <c r="D28" t="s">
+        <v>810</v>
+      </c>
+      <c r="E28" t="s">
+        <v>811</v>
+      </c>
+      <c r="F28" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>812</v>
+      </c>
+      <c r="B29" t="s">
+        <v>574</v>
+      </c>
+      <c r="C29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" t="s">
+        <v>810</v>
+      </c>
+      <c r="E29" t="s">
+        <v>813</v>
+      </c>
+      <c r="F29" t="s">
+        <v>761</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>